--- a/KatalonData/EmailTextToPay/ManualEntry_CANAmount_Upgrade.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry_CANAmount_Upgrade.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="114">
   <si>
     <t>Result</t>
   </si>
@@ -349,6 +349,36 @@
   </si>
   <si>
     <t>Mon Jul 13 19:15:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:15:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:16:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:17:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:17:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:18:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:19:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:20:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:20:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:21:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:22:27 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1016,7 +1046,7 @@
         <v>47</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>33</v>
@@ -1055,7 +1085,7 @@
         <v>47</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C4" s="16" t="s">
         <v>44</v>
@@ -1096,7 +1126,7 @@
         <v>47</v>
       </c>
       <c r="B5" t="s" s="1">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>45</v>
@@ -1137,7 +1167,7 @@
         <v>47</v>
       </c>
       <c r="B6" t="s" s="1">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>49</v>
@@ -1202,7 +1232,7 @@
         <v>47</v>
       </c>
       <c r="B7" t="s" s="1">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>50</v>
@@ -1414,7 +1444,7 @@
         <v>47</v>
       </c>
       <c r="B2" t="s" s="5">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>27</v>
@@ -1458,7 +1488,7 @@
         <v>47</v>
       </c>
       <c r="B3" t="s" s="5">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>30</v>
@@ -1529,7 +1559,7 @@
         <v>47</v>
       </c>
       <c r="B4" t="s" s="5">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>31</v>
@@ -1570,7 +1600,7 @@
         <v>47</v>
       </c>
       <c r="B5" t="s" s="5">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>32</v>
@@ -1612,7 +1642,7 @@
         <v>47</v>
       </c>
       <c r="B6" t="s" s="5">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C6" s="16" t="s">
         <v>46</v>
